--- a/artfynd/A 46898-2025 artfynd.xlsx
+++ b/artfynd/A 46898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303151</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46898-2025 artfynd.xlsx
+++ b/artfynd/A 46898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303151</v>
       </c>
       <c r="B2" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46898-2025 artfynd.xlsx
+++ b/artfynd/A 46898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303151</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46898-2025 artfynd.xlsx
+++ b/artfynd/A 46898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303151</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46898-2025 artfynd.xlsx
+++ b/artfynd/A 46898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303151</v>
       </c>
       <c r="B2" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46898-2025 artfynd.xlsx
+++ b/artfynd/A 46898-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131303151</v>
+        <v>133217977</v>
       </c>
       <c r="B2" t="n">
-        <v>58063</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Erik-Jonsberget, Ång</t>
+          <t>Högkälen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586124</v>
+        <v>586231</v>
       </c>
       <c r="R2" t="n">
-        <v>7010875</v>
+        <v>7011041</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,27 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Observationen är gjord i samband med fågelinventeringar i SvK:s projekt Inlandspaktet.</t>
+          <t>Avbarkningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,15 +780,131 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131303151</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Erik-Jonsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>586124</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7010875</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Observationen är gjord i samband med fågelinventeringar i SvK:s projekt Inlandspaktet.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Janne Dahlén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Janne Dahlén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46898-2025 artfynd.xlsx
+++ b/artfynd/A 46898-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133217977</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,8 +915,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131303151</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>